--- a/docs/perechen-otchetov/obrazcy/ФО-02.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-02.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -826,29 +826,29 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>108370</v>
+        <v>120550</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>106870</v>
+        <v>119050</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="8" t="n">
-        <v>47987.65</v>
+        <v>55169.65</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>71242.28840999999</v>
+        <v>78562.67193500001</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>67729.5</v>
+        <v>75037.5</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>2970.93841</v>
+        <v>2983.321935</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>541.85</v>
@@ -1785,7 +1785,7 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Эко-Продукт»</t>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
         </is>
       </c>
       <c r="B29" s="19" t="n"/>
@@ -2842,29 +2842,29 @@
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>46075</v>
+        <v>58255</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>46075</v>
+        <v>58255</v>
       </c>
       <c r="F52" s="13" t="n"/>
       <c r="G52" s="12" t="n">
-        <v>23140.3</v>
+        <v>30322.3</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>27897.482495</v>
+        <v>35217.824895</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>26950</v>
+        <v>34258</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>836.832495</v>
+        <v>849.174895</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>110.65</v>
@@ -2889,29 +2889,29 @@
         </is>
       </c>
       <c r="B53" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>4500</v>
+        <v>16680</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>4500</v>
+        <v>16680</v>
       </c>
       <c r="F53" s="17" t="n"/>
       <c r="G53" s="16" t="n">
-        <v>636</v>
+        <v>7818</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>3910.685</v>
+        <v>11231.0274</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>3900</v>
+        <v>11208</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>10.685</v>
+        <v>23.0274</v>
       </c>
       <c r="K53" s="16" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Ала-Тоо Агро»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B54" s="19" t="n"/>
@@ -2940,23 +2940,23 @@
         <v>1</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>4500</v>
+        <v>12180</v>
       </c>
       <c r="E54" s="21" t="n">
-        <v>4500</v>
+        <v>12180</v>
       </c>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="21" t="n">
-        <v>636</v>
+        <v>7182</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>3910.685</v>
+        <v>7320.3424</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>3900</v>
+        <v>7308</v>
       </c>
       <c r="J54" s="21" t="n">
-        <v>10.685</v>
+        <v>12.3424</v>
       </c>
       <c r="K54" s="21" t="n">
         <v>0</v>
@@ -2977,31 +2977,31 @@
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>№ 25-4/030 от 10.02.2025, KGS</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="24" t="n"/>
       <c r="D55" s="25" t="n">
-        <v>4500</v>
+        <v>12180</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>4500</v>
+        <v>12180</v>
       </c>
       <c r="F55" s="26" t="n">
-        <v>47462</v>
+        <v>47016</v>
       </c>
       <c r="G55" s="25" t="n">
-        <v>636</v>
+        <v>7182</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>3910.685</v>
+        <v>7320.3424</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>3900</v>
+        <v>7308</v>
       </c>
       <c r="J55" s="25" t="n">
-        <v>10.685</v>
+        <v>12.3424</v>
       </c>
       <c r="K55" s="25" t="n">
         <v>0</v>
@@ -3020,56 +3020,52 @@
       </c>
     </row>
     <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Жайылский р-н</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="F56" s="17" t="n"/>
-      <c r="G56" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="H56" s="16" t="n">
-        <v>711.537</v>
-      </c>
-      <c r="I56" s="16" t="n">
-        <v>650</v>
-      </c>
-      <c r="J56" s="16" t="n">
-        <v>43.137</v>
-      </c>
-      <c r="K56" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="L56" s="16" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="M56" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="N56" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="O56" s="16" t="n">
-        <v>18.4</v>
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,50000)</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="n"/>
+      <c r="C56" s="28" t="n"/>
+      <c r="D56" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="F56" s="30" t="n"/>
+      <c r="G56" s="29" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H56" s="29" t="n">
+        <v>72.1216</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>72</v>
+      </c>
+      <c r="J56" s="29" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="K56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>КФХ «Жайыл»</t>
+          <t>ОсОО «Ала-Тоо Агро»</t>
         </is>
       </c>
       <c r="B57" s="19" t="n"/>
@@ -3077,89 +3073,89 @@
         <v>1</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>800</v>
+        <v>4500</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>800</v>
+        <v>4500</v>
       </c>
       <c r="F57" s="22" t="n"/>
       <c r="G57" s="21" t="n">
-        <v>168</v>
+        <v>636</v>
       </c>
       <c r="H57" s="21" t="n">
-        <v>711.537</v>
+        <v>3910.685</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>650</v>
+        <v>3900</v>
       </c>
       <c r="J57" s="21" t="n">
-        <v>43.137</v>
+        <v>10.685</v>
       </c>
       <c r="K57" s="21" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="L57" s="21" t="n">
-        <v>149.4</v>
+        <v>0</v>
       </c>
       <c r="M57" s="21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N57" s="21" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O57" s="21" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
         <is>
-          <t>№ 23-4/008 от 20.06.2023, KGS</t>
+          <t>№ 25-4/030 от 10.02.2025, KGS</t>
         </is>
       </c>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="24" t="n"/>
       <c r="D58" s="25" t="n">
-        <v>800</v>
+        <v>4500</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>800</v>
+        <v>4500</v>
       </c>
       <c r="F58" s="26" t="n">
-        <v>46861</v>
+        <v>47462</v>
       </c>
       <c r="G58" s="25" t="n">
-        <v>168</v>
+        <v>636</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>711.537</v>
+        <v>3910.685</v>
       </c>
       <c r="I58" s="25" t="n">
-        <v>650</v>
+        <v>3900</v>
       </c>
       <c r="J58" s="25" t="n">
-        <v>43.137</v>
+        <v>10.685</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>149.4</v>
+        <v>0</v>
       </c>
       <c r="M58" s="25" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N58" s="25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O58" s="25" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>г. Кара-Балта</t>
+          <t>Жайылский р-н</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
@@ -3169,44 +3165,44 @@
         <v>1</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F59" s="17" t="n"/>
       <c r="G59" s="16" t="n">
-        <v>1344</v>
+        <v>168</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>1808.877</v>
+        <v>711.537</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="J59" s="16" t="n">
-        <v>8.877000000000001</v>
+        <v>43.137</v>
       </c>
       <c r="K59" s="16" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="L59" s="16" t="n">
-        <v>0</v>
+        <v>149.4</v>
       </c>
       <c r="M59" s="16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N59" s="16" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Кара-Балта Мел»</t>
+          <t>КФХ «Жайыл»</t>
         </is>
       </c>
       <c r="B60" s="19" t="n"/>
@@ -3214,768 +3210,772 @@
         <v>1</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F60" s="22" t="n"/>
       <c r="G60" s="21" t="n">
-        <v>1344</v>
+        <v>168</v>
       </c>
       <c r="H60" s="21" t="n">
-        <v>1808.877</v>
+        <v>711.537</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="J60" s="21" t="n">
-        <v>8.877000000000001</v>
+        <v>43.137</v>
       </c>
       <c r="K60" s="21" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="L60" s="21" t="n">
-        <v>0</v>
+        <v>149.4</v>
       </c>
       <c r="M60" s="21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N60" s="21" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O60" s="21" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>№ 20-2/090 от 12.08.2020, KGS</t>
+          <t>№ 23-4/008 от 20.06.2023, KGS</t>
         </is>
       </c>
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="24" t="n"/>
       <c r="D61" s="25" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F61" s="26" t="n">
-        <v>47342</v>
+        <v>46861</v>
       </c>
       <c r="G61" s="25" t="n">
-        <v>1344</v>
+        <v>168</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>1808.877</v>
+        <v>711.537</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="J61" s="25" t="n">
-        <v>8.877000000000001</v>
+        <v>43.137</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>0</v>
+        <v>149.4</v>
       </c>
       <c r="M61" s="25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N61" s="25" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O61" s="25" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Кеминский р-н</t>
+          <t>г. Кара-Балта</t>
         </is>
       </c>
       <c r="B62" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="16" t="n">
-        <v>28875</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="16" t="n">
-        <v>28875</v>
+        <v>3000</v>
       </c>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="16" t="n">
-        <v>16622.3</v>
+        <v>1344</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>16338.541495</v>
+        <v>1808.877</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>15500</v>
+        <v>1800</v>
       </c>
       <c r="J62" s="16" t="n">
-        <v>746.2914950000001</v>
+        <v>8.877000000000001</v>
       </c>
       <c r="K62" s="16" t="n">
-        <v>92.25</v>
+        <v>0</v>
       </c>
       <c r="L62" s="16" t="n">
-        <v>2934.5</v>
+        <v>0</v>
       </c>
       <c r="M62" s="16" t="n">
-        <v>2150</v>
+        <v>0</v>
       </c>
       <c r="N62" s="16" t="n">
-        <v>692.25</v>
+        <v>0</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>92.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Кемин-Курулуш»</t>
+          <t>ОсОО «Кара-Балта Мел»</t>
         </is>
       </c>
       <c r="B63" s="19" t="n"/>
       <c r="C63" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>28875</v>
+        <v>3000</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>28875</v>
+        <v>3000</v>
       </c>
       <c r="F63" s="22" t="n"/>
       <c r="G63" s="21" t="n">
-        <v>16622.3</v>
+        <v>1344</v>
       </c>
       <c r="H63" s="21" t="n">
-        <v>16338.541495</v>
+        <v>1808.877</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>15500</v>
+        <v>1800</v>
       </c>
       <c r="J63" s="21" t="n">
-        <v>746.2914950000001</v>
+        <v>8.877000000000001</v>
       </c>
       <c r="K63" s="21" t="n">
-        <v>92.25</v>
+        <v>0</v>
       </c>
       <c r="L63" s="21" t="n">
-        <v>2934.5</v>
+        <v>0</v>
       </c>
       <c r="M63" s="21" t="n">
-        <v>2150</v>
+        <v>0</v>
       </c>
       <c r="N63" s="21" t="n">
-        <v>692.25</v>
+        <v>0</v>
       </c>
       <c r="O63" s="21" t="n">
-        <v>92.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>№ 19-3/061 от 11.04.2019, USD</t>
+          <t>№ 20-2/090 от 12.08.2020, KGS</t>
         </is>
       </c>
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="24" t="n"/>
       <c r="D64" s="25" t="n">
-        <v>21875</v>
+        <v>3000</v>
       </c>
       <c r="E64" s="25" t="n">
-        <v>21875</v>
+        <v>3000</v>
       </c>
       <c r="F64" s="26" t="n">
-        <v>47219</v>
+        <v>47342</v>
       </c>
       <c r="G64" s="25" t="n">
-        <v>13412.3</v>
+        <v>1344</v>
       </c>
       <c r="H64" s="25" t="n">
-        <v>11160.205875</v>
+        <v>1808.877</v>
       </c>
       <c r="I64" s="25" t="n">
-        <v>10500</v>
+        <v>1800</v>
       </c>
       <c r="J64" s="25" t="n">
-        <v>581.455875</v>
+        <v>8.877000000000001</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
       <c r="L64" s="25" t="n">
-        <v>2380</v>
+        <v>0</v>
       </c>
       <c r="M64" s="25" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="N64" s="25" t="n">
-        <v>551.25</v>
+        <v>0</v>
       </c>
       <c r="O64" s="25" t="n">
-        <v>78.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>в тыс. USD (курс 87,50000)</t>
-        </is>
-      </c>
-      <c r="B65" s="28" t="n"/>
-      <c r="C65" s="28" t="n"/>
-      <c r="D65" s="29" t="n">
-        <v>250</v>
-      </c>
-      <c r="E65" s="29" t="n">
-        <v>250</v>
-      </c>
-      <c r="F65" s="30" t="n"/>
-      <c r="G65" s="29" t="n">
-        <v>171.2</v>
-      </c>
-      <c r="H65" s="29" t="n">
-        <v>127.54521</v>
-      </c>
-      <c r="I65" s="29" t="n">
-        <v>120</v>
-      </c>
-      <c r="J65" s="29" t="n">
-        <v>6.64521</v>
-      </c>
-      <c r="K65" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L65" s="29" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="M65" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="N65" s="29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O65" s="29" t="n">
-        <v>0.9</v>
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Кеминский р-н</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>28875</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>28875</v>
+      </c>
+      <c r="F65" s="17" t="n"/>
+      <c r="G65" s="16" t="n">
+        <v>16622.3</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>16338.541495</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>15500</v>
+      </c>
+      <c r="J65" s="16" t="n">
+        <v>746.2914950000001</v>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="L65" s="16" t="n">
+        <v>2934.5</v>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N65" s="16" t="n">
+        <v>692.25</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>92.25</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="23" t="inlineStr">
-        <is>
-          <t>№ 22-3/014 от 18.03.2022, KGS</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="n"/>
-      <c r="C66" s="24" t="n"/>
-      <c r="D66" s="25" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E66" s="25" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F66" s="26" t="n">
-        <v>47560</v>
-      </c>
-      <c r="G66" s="25" t="n">
-        <v>2850</v>
-      </c>
-      <c r="H66" s="25" t="n">
-        <v>3324.83836</v>
-      </c>
-      <c r="I66" s="25" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J66" s="25" t="n">
-        <v>112.43836</v>
-      </c>
-      <c r="K66" s="25" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L66" s="25" t="n">
-        <v>508.4</v>
-      </c>
-      <c r="M66" s="25" t="n">
-        <v>400</v>
-      </c>
-      <c r="N66" s="25" t="n">
-        <v>96</v>
-      </c>
-      <c r="O66" s="25" t="n">
-        <v>12.4</v>
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="21" t="n">
+        <v>28875</v>
+      </c>
+      <c r="E66" s="21" t="n">
+        <v>28875</v>
+      </c>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="21" t="n">
+        <v>16622.3</v>
+      </c>
+      <c r="H66" s="21" t="n">
+        <v>16338.541495</v>
+      </c>
+      <c r="I66" s="21" t="n">
+        <v>15500</v>
+      </c>
+      <c r="J66" s="21" t="n">
+        <v>746.2914950000001</v>
+      </c>
+      <c r="K66" s="21" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="L66" s="21" t="n">
+        <v>2934.5</v>
+      </c>
+      <c r="M66" s="21" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N66" s="21" t="n">
+        <v>692.25</v>
+      </c>
+      <c r="O66" s="21" t="n">
+        <v>92.25</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>№ 24-3/105 от 02.12.2024, KGS</t>
+          <t>№ 19-3/061 от 11.04.2019, USD</t>
         </is>
       </c>
       <c r="B67" s="24" t="n"/>
       <c r="C67" s="24" t="n"/>
       <c r="D67" s="25" t="n">
-        <v>2000</v>
+        <v>21875</v>
       </c>
       <c r="E67" s="25" t="n">
-        <v>2000</v>
+        <v>21875</v>
       </c>
       <c r="F67" s="26" t="n">
-        <v>48184</v>
+        <v>47219</v>
       </c>
       <c r="G67" s="25" t="n">
-        <v>360</v>
+        <v>13412.3</v>
       </c>
       <c r="H67" s="25" t="n">
-        <v>1853.49726</v>
+        <v>11160.205875</v>
       </c>
       <c r="I67" s="25" t="n">
-        <v>1800</v>
+        <v>10500</v>
       </c>
       <c r="J67" s="25" t="n">
-        <v>52.39726</v>
+        <v>581.455875</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>1.1</v>
+        <v>78.75</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>46.1</v>
+        <v>2380</v>
       </c>
       <c r="M67" s="25" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="N67" s="25" t="n">
-        <v>45</v>
+        <v>551.25</v>
       </c>
       <c r="O67" s="25" t="n">
-        <v>1.1</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Сокулукский р-н</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>8900</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>8900</v>
-      </c>
-      <c r="F68" s="17" t="n"/>
-      <c r="G68" s="16" t="n">
-        <v>4370</v>
-      </c>
-      <c r="H68" s="16" t="n">
-        <v>5127.842</v>
-      </c>
-      <c r="I68" s="16" t="n">
-        <v>5100</v>
-      </c>
-      <c r="J68" s="16" t="n">
-        <v>27.842</v>
-      </c>
-      <c r="K68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="16" t="n">
-        <v>0</v>
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="29" t="n">
+        <v>250</v>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>250</v>
+      </c>
+      <c r="F68" s="30" t="n"/>
+      <c r="G68" s="29" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="H68" s="29" t="n">
+        <v>127.54521</v>
+      </c>
+      <c r="I68" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="J68" s="29" t="n">
+        <v>6.64521</v>
+      </c>
+      <c r="K68" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L68" s="29" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="M68" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="N68" s="29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O68" s="29" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Ак-Дан»</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="n"/>
-      <c r="C69" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" s="21" t="n">
-        <v>8900</v>
-      </c>
-      <c r="E69" s="21" t="n">
-        <v>8900</v>
-      </c>
-      <c r="F69" s="22" t="n"/>
-      <c r="G69" s="21" t="n">
-        <v>4370</v>
-      </c>
-      <c r="H69" s="21" t="n">
-        <v>5127.842</v>
-      </c>
-      <c r="I69" s="21" t="n">
-        <v>5100</v>
-      </c>
-      <c r="J69" s="21" t="n">
-        <v>27.842</v>
-      </c>
-      <c r="K69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="21" t="n">
-        <v>0</v>
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>№ 22-3/014 от 18.03.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="n"/>
+      <c r="C69" s="24" t="n"/>
+      <c r="D69" s="25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E69" s="25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F69" s="26" t="n">
+        <v>47560</v>
+      </c>
+      <c r="G69" s="25" t="n">
+        <v>2850</v>
+      </c>
+      <c r="H69" s="25" t="n">
+        <v>3324.83836</v>
+      </c>
+      <c r="I69" s="25" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J69" s="25" t="n">
+        <v>112.43836</v>
+      </c>
+      <c r="K69" s="25" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L69" s="25" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="M69" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="N69" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="O69" s="25" t="n">
+        <v>12.4</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>№ 21-3/117 от 15.04.2021, KGS</t>
+          <t>№ 24-3/105 от 02.12.2024, KGS</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="24" t="n"/>
       <c r="D70" s="25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E70" s="25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <v>48184</v>
+      </c>
+      <c r="G70" s="25" t="n">
+        <v>360</v>
+      </c>
+      <c r="H70" s="25" t="n">
+        <v>1853.49726</v>
+      </c>
+      <c r="I70" s="25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J70" s="25" t="n">
+        <v>52.39726</v>
+      </c>
+      <c r="K70" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L70" s="25" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="M70" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="O70" s="25" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="71" ht="13" customHeight="1">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Сокулукский р-н</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F71" s="17" t="n"/>
+      <c r="G71" s="16" t="n">
+        <v>4370</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>5127.842</v>
+      </c>
+      <c r="I71" s="16" t="n">
+        <v>5100</v>
+      </c>
+      <c r="J71" s="16" t="n">
+        <v>27.842</v>
+      </c>
+      <c r="K71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="13" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Ак-Дан»</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="21" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E72" s="21" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F72" s="22" t="n"/>
+      <c r="G72" s="21" t="n">
+        <v>4370</v>
+      </c>
+      <c r="H72" s="21" t="n">
+        <v>5127.842</v>
+      </c>
+      <c r="I72" s="21" t="n">
+        <v>5100</v>
+      </c>
+      <c r="J72" s="21" t="n">
+        <v>27.842</v>
+      </c>
+      <c r="K72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="13" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>№ 21-3/117 от 15.04.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="n"/>
+      <c r="C73" s="24" t="n"/>
+      <c r="D73" s="25" t="n">
         <v>6500</v>
       </c>
-      <c r="E70" s="25" t="n">
+      <c r="E73" s="25" t="n">
         <v>6500</v>
       </c>
-      <c r="F70" s="26" t="n">
+      <c r="F73" s="26" t="n">
         <v>47192</v>
       </c>
-      <c r="G70" s="25" t="n">
+      <c r="G73" s="25" t="n">
         <v>2990</v>
       </c>
-      <c r="H70" s="25" t="n">
+      <c r="H73" s="25" t="n">
         <v>3920.034</v>
       </c>
-      <c r="I70" s="25" t="n">
+      <c r="I73" s="25" t="n">
         <v>3900</v>
       </c>
-      <c r="J70" s="25" t="n">
+      <c r="J73" s="25" t="n">
         <v>20.034</v>
       </c>
-      <c r="K70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="23" t="inlineStr">
+      <c r="K73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1">
+      <c r="A74" s="23" t="inlineStr">
         <is>
           <t>№ 22-2/031 от 11.03.2022, KGS</t>
         </is>
       </c>
-      <c r="B71" s="24" t="n"/>
-      <c r="C71" s="24" t="n"/>
-      <c r="D71" s="25" t="n">
+      <c r="B74" s="24" t="n"/>
+      <c r="C74" s="24" t="n"/>
+      <c r="D74" s="25" t="n">
         <v>2400</v>
       </c>
-      <c r="E71" s="25" t="n">
+      <c r="E74" s="25" t="n">
         <v>2400</v>
       </c>
-      <c r="F71" s="26" t="n">
+      <c r="F74" s="26" t="n">
         <v>46641</v>
       </c>
-      <c r="G71" s="25" t="n">
+      <c r="G74" s="25" t="n">
         <v>1380</v>
       </c>
-      <c r="H71" s="25" t="n">
+      <c r="H74" s="25" t="n">
         <v>1207.808</v>
       </c>
-      <c r="I71" s="25" t="n">
+      <c r="I74" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="J71" s="25" t="n">
+      <c r="J74" s="25" t="n">
         <v>7.808</v>
       </c>
-      <c r="K71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="K74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>г. Бишкек</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n">
+      <c r="B75" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C72" s="11" t="n">
+      <c r="C75" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D72" s="12" t="n">
+      <c r="D75" s="12" t="n">
         <v>11750</v>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="E75" s="12" t="n">
         <v>11750</v>
       </c>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="12" t="n">
+      <c r="F75" s="13" t="n"/>
+      <c r="G75" s="12" t="n">
         <v>5533.35</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>6775.490625</v>
-      </c>
-      <c r="I72" s="12" t="n">
+      <c r="H75" s="12" t="n">
+        <v>6775.53175</v>
+      </c>
+      <c r="I75" s="12" t="n">
         <v>6712.5</v>
       </c>
-      <c r="J72" s="12" t="n">
-        <v>60.640625</v>
-      </c>
-      <c r="K72" s="12" t="n">
+      <c r="J75" s="12" t="n">
+        <v>60.68175</v>
+      </c>
+      <c r="K75" s="12" t="n">
         <v>2.35</v>
       </c>
-      <c r="L72" s="12" t="n">
+      <c r="L75" s="12" t="n">
         <v>180.85</v>
       </c>
-      <c r="M72" s="12" t="n">
+      <c r="M75" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="N72" s="12" t="n">
+      <c r="N75" s="12" t="n">
         <v>28.5</v>
       </c>
-      <c r="O72" s="12" t="n">
+      <c r="O75" s="12" t="n">
         <v>2.35</v>
       </c>
     </row>
-    <row r="73" ht="13" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>г. Бишкек</t>
         </is>
       </c>
-      <c r="B73" s="15" t="n">
+      <c r="B76" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="15" t="n">
+      <c r="C76" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D76" s="16" t="n">
         <v>11750</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E76" s="16" t="n">
         <v>11750</v>
       </c>
-      <c r="F73" s="17" t="n"/>
-      <c r="G73" s="16" t="n">
+      <c r="F76" s="17" t="n"/>
+      <c r="G76" s="16" t="n">
         <v>5533.35</v>
       </c>
-      <c r="H73" s="16" t="n">
-        <v>6775.490625</v>
-      </c>
-      <c r="I73" s="16" t="n">
+      <c r="H76" s="16" t="n">
+        <v>6775.53175</v>
+      </c>
+      <c r="I76" s="16" t="n">
         <v>6712.5</v>
       </c>
-      <c r="J73" s="16" t="n">
-        <v>60.640625</v>
-      </c>
-      <c r="K73" s="16" t="n">
+      <c r="J76" s="16" t="n">
+        <v>60.68175</v>
+      </c>
+      <c r="K76" s="16" t="n">
         <v>2.35</v>
       </c>
-      <c r="L73" s="16" t="n">
+      <c r="L76" s="16" t="n">
         <v>180.85</v>
       </c>
-      <c r="M73" s="16" t="n">
+      <c r="M76" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N76" s="16" t="n">
         <v>28.5</v>
       </c>
-      <c r="O73" s="16" t="n">
+      <c r="O76" s="16" t="n">
         <v>2.35</v>
-      </c>
-    </row>
-    <row r="74" ht="13" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Кут-Мүлк»</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="n"/>
-      <c r="C74" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="21" t="n">
-        <v>8750</v>
-      </c>
-      <c r="E74" s="21" t="n">
-        <v>8750</v>
-      </c>
-      <c r="F74" s="22" t="n"/>
-      <c r="G74" s="21" t="n">
-        <v>4268.35</v>
-      </c>
-      <c r="H74" s="21" t="n">
-        <v>4832.277625</v>
-      </c>
-      <c r="I74" s="21" t="n">
-        <v>4812.5</v>
-      </c>
-      <c r="J74" s="21" t="n">
-        <v>19.777625</v>
-      </c>
-      <c r="K74" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="13" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
-        <is>
-          <t>№ 23-1/019 от 05.05.2023, USD</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="n"/>
-      <c r="C75" s="24" t="n"/>
-      <c r="D75" s="25" t="n">
-        <v>8750</v>
-      </c>
-      <c r="E75" s="25" t="n">
-        <v>8750</v>
-      </c>
-      <c r="F75" s="26" t="n">
-        <v>46604</v>
-      </c>
-      <c r="G75" s="25" t="n">
-        <v>4268.35</v>
-      </c>
-      <c r="H75" s="25" t="n">
-        <v>4832.277625</v>
-      </c>
-      <c r="I75" s="25" t="n">
-        <v>4812.5</v>
-      </c>
-      <c r="J75" s="25" t="n">
-        <v>19.777625</v>
-      </c>
-      <c r="K75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="13" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
-        <is>
-          <t>в тыс. USD (курс 87,50000)</t>
-        </is>
-      </c>
-      <c r="B76" s="28" t="n"/>
-      <c r="C76" s="28" t="n"/>
-      <c r="D76" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E76" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="F76" s="30" t="n"/>
-      <c r="G76" s="29" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="H76" s="29" t="n">
-        <v>55.22603</v>
-      </c>
-      <c r="I76" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="J76" s="29" t="n">
-        <v>0.22603</v>
-      </c>
-      <c r="K76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77" ht="13" customHeight="1">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Тянь-Шань Строй»</t>
+          <t>ОсОО «Кут-Мүлк»</t>
         </is>
       </c>
       <c r="B77" s="19" t="n"/>
@@ -3983,309 +3983,442 @@
         <v>1</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>3000</v>
+        <v>8750</v>
       </c>
       <c r="E77" s="21" t="n">
-        <v>3000</v>
+        <v>8750</v>
       </c>
       <c r="F77" s="22" t="n"/>
       <c r="G77" s="21" t="n">
-        <v>1265</v>
+        <v>4268.35</v>
       </c>
       <c r="H77" s="21" t="n">
-        <v>1943.213</v>
+        <v>4832.31875</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>1900</v>
+        <v>4812.5</v>
       </c>
       <c r="J77" s="21" t="n">
-        <v>40.863</v>
+        <v>19.81875</v>
       </c>
       <c r="K77" s="21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>180.85</v>
+        <v>0</v>
       </c>
       <c r="M77" s="21" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N77" s="21" t="n">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="13" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>№ 22-1/045 от 03.02.2022, KGS</t>
+          <t>№ 23-1/019 от 05.05.2023, USD</t>
         </is>
       </c>
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="24" t="n"/>
       <c r="D78" s="25" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E78" s="25" t="n">
+        <v>8750</v>
+      </c>
+      <c r="F78" s="26" t="n">
+        <v>46604</v>
+      </c>
+      <c r="G78" s="25" t="n">
+        <v>4268.35</v>
+      </c>
+      <c r="H78" s="25" t="n">
+        <v>4832.31875</v>
+      </c>
+      <c r="I78" s="25" t="n">
+        <v>4812.5</v>
+      </c>
+      <c r="J78" s="25" t="n">
+        <v>19.81875</v>
+      </c>
+      <c r="K78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="13" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B79" s="28" t="n"/>
+      <c r="C79" s="28" t="n"/>
+      <c r="D79" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E79" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F79" s="30" t="n"/>
+      <c r="G79" s="29" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="H79" s="29" t="n">
+        <v>55.2265</v>
+      </c>
+      <c r="I79" s="29" t="n">
+        <v>55</v>
+      </c>
+      <c r="J79" s="29" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="K79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="13" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Строй»</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="E78" s="25" t="n">
+      <c r="E80" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="F78" s="26" t="n">
+      <c r="F80" s="22" t="n"/>
+      <c r="G80" s="21" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H80" s="21" t="n">
+        <v>1943.213</v>
+      </c>
+      <c r="I80" s="21" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J80" s="21" t="n">
+        <v>40.863</v>
+      </c>
+      <c r="K80" s="21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L80" s="21" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="M80" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="N80" s="21" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O80" s="21" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="81" ht="13" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>№ 22-1/045 от 03.02.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="n"/>
+      <c r="C81" s="24" t="n"/>
+      <c r="D81" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F81" s="26" t="n">
         <v>46641</v>
       </c>
-      <c r="G78" s="25" t="n">
+      <c r="G81" s="25" t="n">
         <v>1265</v>
       </c>
-      <c r="H78" s="25" t="n">
+      <c r="H81" s="25" t="n">
         <v>1943.213</v>
       </c>
-      <c r="I78" s="25" t="n">
+      <c r="I81" s="25" t="n">
         <v>1900</v>
       </c>
-      <c r="J78" s="25" t="n">
+      <c r="J81" s="25" t="n">
         <v>40.863</v>
       </c>
-      <c r="K78" s="25" t="n">
+      <c r="K81" s="25" t="n">
         <v>2.35</v>
       </c>
-      <c r="L78" s="25" t="n">
+      <c r="L81" s="25" t="n">
         <v>180.85</v>
       </c>
-      <c r="M78" s="25" t="n">
+      <c r="M81" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="N78" s="25" t="n">
+      <c r="N81" s="25" t="n">
         <v>28.5</v>
       </c>
-      <c r="O78" s="25" t="n">
+      <c r="O81" s="25" t="n">
         <v>2.35</v>
       </c>
     </row>
-    <row r="79" ht="13" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
+    <row r="82" ht="13" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>г. Ош</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="12" t="n">
+      <c r="B82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="12" t="n">
         <v>8120</v>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="E82" s="12" t="n">
         <v>8120</v>
       </c>
-      <c r="F79" s="13" t="n"/>
-      <c r="G79" s="12" t="n">
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="12" t="n">
         <v>4222.8</v>
       </c>
-      <c r="H79" s="12" t="n">
+      <c r="H82" s="12" t="n">
         <v>5133.70354</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="I82" s="12" t="n">
         <v>4872</v>
       </c>
-      <c r="J79" s="12" t="n">
+      <c r="J82" s="12" t="n">
         <v>231.25354</v>
       </c>
-      <c r="K79" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>30.45</v>
       </c>
-      <c r="L79" s="12" t="n">
+      <c r="L82" s="12" t="n">
         <v>1061.69</v>
       </c>
-      <c r="M79" s="12" t="n">
+      <c r="M82" s="12" t="n">
         <v>812</v>
       </c>
-      <c r="N79" s="12" t="n">
+      <c r="N82" s="12" t="n">
         <v>219.24</v>
       </c>
-      <c r="O79" s="12" t="n">
+      <c r="O82" s="12" t="n">
         <v>30.45</v>
       </c>
     </row>
-    <row r="80" ht="13" customHeight="1">
-      <c r="A80" s="14" t="inlineStr">
+    <row r="83" ht="13" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t>г. Ош</t>
         </is>
       </c>
-      <c r="B80" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="16" t="n">
+      <c r="B83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="16" t="n">
         <v>8120</v>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E83" s="16" t="n">
         <v>8120</v>
       </c>
-      <c r="F80" s="17" t="n"/>
-      <c r="G80" s="16" t="n">
+      <c r="F83" s="17" t="n"/>
+      <c r="G83" s="16" t="n">
         <v>4222.8</v>
       </c>
-      <c r="H80" s="16" t="n">
+      <c r="H83" s="16" t="n">
         <v>5133.70354</v>
       </c>
-      <c r="I80" s="16" t="n">
+      <c r="I83" s="16" t="n">
         <v>4872</v>
       </c>
-      <c r="J80" s="16" t="n">
+      <c r="J83" s="16" t="n">
         <v>231.25354</v>
       </c>
-      <c r="K80" s="16" t="n">
+      <c r="K83" s="16" t="n">
         <v>30.45</v>
       </c>
-      <c r="L80" s="16" t="n">
+      <c r="L83" s="16" t="n">
         <v>1061.69</v>
       </c>
-      <c r="M80" s="16" t="n">
+      <c r="M83" s="16" t="n">
         <v>812</v>
       </c>
-      <c r="N80" s="16" t="n">
+      <c r="N83" s="16" t="n">
         <v>219.24</v>
       </c>
-      <c r="O80" s="16" t="n">
+      <c r="O83" s="16" t="n">
         <v>30.45</v>
       </c>
     </row>
-    <row r="81" ht="13" customHeight="1">
-      <c r="A81" s="18" t="inlineStr">
+    <row r="84" ht="13" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Сулайман-Тоо Трейд»</t>
         </is>
       </c>
-      <c r="B81" s="19" t="n"/>
-      <c r="C81" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="21" t="n">
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="21" t="n">
         <v>8120</v>
       </c>
-      <c r="E81" s="21" t="n">
+      <c r="E84" s="21" t="n">
         <v>8120</v>
       </c>
-      <c r="F81" s="22" t="n"/>
-      <c r="G81" s="21" t="n">
+      <c r="F84" s="22" t="n"/>
+      <c r="G84" s="21" t="n">
         <v>4222.8</v>
       </c>
-      <c r="H81" s="21" t="n">
+      <c r="H84" s="21" t="n">
         <v>5133.70354</v>
       </c>
-      <c r="I81" s="21" t="n">
+      <c r="I84" s="21" t="n">
         <v>4872</v>
       </c>
-      <c r="J81" s="21" t="n">
+      <c r="J84" s="21" t="n">
         <v>231.25354</v>
       </c>
-      <c r="K81" s="21" t="n">
+      <c r="K84" s="21" t="n">
         <v>30.45</v>
       </c>
-      <c r="L81" s="21" t="n">
+      <c r="L84" s="21" t="n">
         <v>1061.69</v>
       </c>
-      <c r="M81" s="21" t="n">
+      <c r="M84" s="21" t="n">
         <v>812</v>
       </c>
-      <c r="N81" s="21" t="n">
+      <c r="N84" s="21" t="n">
         <v>219.24</v>
       </c>
-      <c r="O81" s="21" t="n">
+      <c r="O84" s="21" t="n">
         <v>30.45</v>
       </c>
     </row>
-    <row r="82" ht="13" customHeight="1">
-      <c r="A82" s="23" t="inlineStr">
+    <row r="85" ht="13" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>№ 21-1/207 от 15.11.2021, EUR</t>
         </is>
       </c>
-      <c r="B82" s="24" t="n"/>
-      <c r="C82" s="24" t="n"/>
-      <c r="D82" s="25" t="n">
+      <c r="B85" s="24" t="n"/>
+      <c r="C85" s="24" t="n"/>
+      <c r="D85" s="25" t="n">
         <v>8120</v>
       </c>
-      <c r="E82" s="25" t="n">
+      <c r="E85" s="25" t="n">
         <v>8120</v>
       </c>
-      <c r="F82" s="26" t="n">
+      <c r="F85" s="26" t="n">
         <v>47072</v>
       </c>
-      <c r="G82" s="25" t="n">
+      <c r="G85" s="25" t="n">
         <v>4222.8</v>
       </c>
-      <c r="H82" s="25" t="n">
+      <c r="H85" s="25" t="n">
         <v>5133.70354</v>
       </c>
-      <c r="I82" s="25" t="n">
+      <c r="I85" s="25" t="n">
         <v>4872</v>
       </c>
-      <c r="J82" s="25" t="n">
+      <c r="J85" s="25" t="n">
         <v>231.25354</v>
       </c>
-      <c r="K82" s="25" t="n">
+      <c r="K85" s="25" t="n">
         <v>30.45</v>
       </c>
-      <c r="L82" s="25" t="n">
+      <c r="L85" s="25" t="n">
         <v>1061.69</v>
       </c>
-      <c r="M82" s="25" t="n">
+      <c r="M85" s="25" t="n">
         <v>812</v>
       </c>
-      <c r="N82" s="25" t="n">
+      <c r="N85" s="25" t="n">
         <v>219.24</v>
       </c>
-      <c r="O82" s="25" t="n">
+      <c r="O85" s="25" t="n">
         <v>30.45</v>
       </c>
     </row>
-    <row r="83" ht="13" customHeight="1">
-      <c r="A83" s="27" t="inlineStr">
+    <row r="86" ht="13" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>в тыс. EUR (курс 101,50000)</t>
         </is>
       </c>
-      <c r="B83" s="28" t="n"/>
-      <c r="C83" s="28" t="n"/>
-      <c r="D83" s="29" t="n">
+      <c r="B86" s="28" t="n"/>
+      <c r="C86" s="28" t="n"/>
+      <c r="D86" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="E83" s="29" t="n">
+      <c r="E86" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="F83" s="30" t="n"/>
-      <c r="G83" s="29" t="n">
+      <c r="F86" s="30" t="n"/>
+      <c r="G86" s="29" t="n">
         <v>45.9</v>
       </c>
-      <c r="H83" s="29" t="n">
+      <c r="H86" s="29" t="n">
         <v>50.57836</v>
       </c>
-      <c r="I83" s="29" t="n">
+      <c r="I86" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="J83" s="29" t="n">
+      <c r="J86" s="29" t="n">
         <v>2.27836</v>
       </c>
-      <c r="K83" s="29" t="n">
+      <c r="K86" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="L83" s="29" t="n">
+      <c r="L86" s="29" t="n">
         <v>10.46</v>
       </c>
-      <c r="M83" s="29" t="n">
+      <c r="M86" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="N83" s="29" t="n">
+      <c r="N86" s="29" t="n">
         <v>2.16</v>
       </c>
-      <c r="O83" s="29" t="n">
+      <c r="O86" s="29" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4470,7 +4603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4930,7 +5063,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="35" t="inlineStr">
         <is>
           <t>1.</t>
@@ -4938,11 +5071,11 @@
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
-          <t>ИТОГО: заёмщиков 20, кредитов 23 — все кредиты набора, у которых на 01.10.2026 основная сумма + проценты + штрафы больше нуля.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>ИТОГО: заёмщиков 21, кредитов 24 — все кредиты набора, у которых на 01.10.2026 основная сумма + проценты + штрафы больше нуля (= ФО-28; ФО-57 — 22 и 25: в нём ещё КЗ-26 с неосвоенной суммой договора).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="35" t="inlineStr">
         <is>
           <t>2.</t>
@@ -4950,7 +5083,7 @@
       </c>
       <c r="B40" s="36" t="inlineStr">
         <is>
-          <t>ИТОГО «по основной сумме» (остаток) = 67 729,500 тыс. сом; «Просроченная задолженность» = 10 347,215 тыс. сом — равна ИТОГО ФО-01 на ту же дату.</t>
+          <t>ИТОГО «по основной сумме» (остаток) = 75 037,500 тыс. сом (= ФО-24 на конец сентября, ФО-25, ФО-28, ФО-57, ФО-59); «Всего остаток» = 78 562,672 (= «Задолженность всего» ФО-57): проценты 2 983,322, штрафы 541,850; «Просроченная задолженность» = 10 347,215 тыс. сом — равна ИТОГО ФО-01 на ту же дату.</t>
         </is>
       </c>
     </row>
@@ -4986,11 +5119,11 @@
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>Валютные кредиты КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): сумма по договору, получено, остаток, просрочка — по курсу на 30.09.2026; погашено — по курсу дня платежей (КЗ-11: 48,200 тыс. USD = 4 268,350 тыс. сом). Под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)», в итоги не входит.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+          <t>Валютные кредиты КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22, КЗ-25 (EUR 101,50000): сумма по договору, получено, остаток, просрочка — по курсу на 30.09.2026; погашено — по курсу дня платежей (КЗ-11: 48,200 тыс. USD = 4 268,350 тыс. сом). Под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)», в итоги не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="35" t="inlineStr">
         <is>
           <t>6.</t>
@@ -4998,43 +5131,43 @@
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
+          <t>КЗ-11 № 23-1/019: проценты на 30.09.2026 0,22650 тыс. USD = 19,819 тыс. сом (на 31.08.2026 0,22615 + начислено 0,27535 − уплачено 05.09.2026 0,27500 = 275,00 USD по курсу 87,40), как в ФО-53 и ФО-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>КЗ-25 № 21-9/040 (EUR, плавающая ставка): остаток 72,000 тыс. EUR = 7 308,000; проценты 121,60 EUR = 12,342 тыс. сом (10 дней с 21.09.2026 по ставке 6,08 %, факт/360); просрочки нет; в разрезе Аламудунский р-н — два заёмщика, «Ала-Арча Энерго» перед «Ала-Тоо Агро».</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="inlineStr">
+        <is>
+          <t>КЗ-07 № 21-6/144: заёмщик на дату — ОсОО «Ысык-Көл Логистик» (долг переведён с ОсОО «Эко-Продукт» 09.09.2026, соглашение № 14), область и район кредита — Иссык-Кульская обл., Тюпский р-н.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
           <t>КЗ-24: основная сумма и проценты погашены, неоплаченные штрафы 18,400 тыс. сом — кредит в отчёте есть, остаток по основной сумме 0,00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="35" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="B45" s="36" t="inlineStr">
-        <is>
-          <t>КЗ-21 — одна строка заёмщика (3 кредита), кредиты по дате договора: 11.04.2019, 18.03.2022, 02.12.2024; КЗ-01 — 15.04.2021, 11.03.2022.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="35" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="B46" s="36" t="inlineStr">
-        <is>
-          <t>У г. Бишкек (КЗ-02, КЗ-11) и г. Ош (КЗ-22) по две строки: область и район.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="35" t="inlineStr">
-        <is>
-          <t>9.</t>
-        </is>
-      </c>
-      <c r="B47" s="36" t="inlineStr">
-        <is>
-          <t>Закрытые кредиты КЗ-08, КЗ-15, КЗ-16, КЗ-18 в отчёте не показаны.</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5179,48 @@
       </c>
       <c r="B48" s="36" t="inlineStr">
         <is>
+          <t>КЗ-21 — одна строка заёмщика (3 кредита), кредиты по дате договора: 11.04.2019, 18.03.2022, 02.12.2024; КЗ-01 — 15.04.2021, 11.03.2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>У г. Бишкек (КЗ-02, КЗ-11) и г. Ош (КЗ-22) по две строки: область и район.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B50" s="36" t="inlineStr">
+        <is>
+          <t>Закрытые кредиты КЗ-08 (списан 17.09.2026), КЗ-15, КЗ-16, КЗ-18 в отчёте не показаны; КЗ-26 № 26-3/118 — зарегистрирован, освоений не было, задолженности нет — тоже не показан.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="inlineStr">
+        <is>
           <t>Отбор «только с просрочкой»: остаются кредиты из ФО-01 на ту же дату (13), итог просрочки тот же.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="29">
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
@@ -5072,10 +5241,13 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
